--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00730-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00730-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3AE8EA1-4F6F-4D5D-B50D-C4A0EB16BA6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1CB1F8A8-7276-4096-ACF9-5F127CEBA4B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{FED55A5B-A9D5-4560-A3FE-306B82803B38}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{E3BCD2AD-2D9A-4550-B9DD-94F257220321}"/>
   </bookViews>
   <sheets>
     <sheet name="00730-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1564,24 +1564,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D1DB567-6FE1-4D74-A4CE-F186B4B298F9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41D37F85-00D4-4144-85DD-5E49C4D11946}">
   <dimension ref="A1:R31"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="11.375" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1609,7 +1610,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1639,7 +1640,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1685,7 +1686,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1735,7 +1736,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1789,7 +1790,7 @@
         <v>5.61</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1815,7 +1816,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>26</v>
       </c>
@@ -1871,7 +1872,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -1927,7 +1928,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="49">
         <v>2025</v>
       </c>
@@ -1981,7 +1982,7 @@
         <v>5.53</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>26</v>
       </c>
@@ -2037,7 +2038,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>26</v>
       </c>
@@ -2093,7 +2094,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>26</v>
       </c>
@@ -2149,7 +2150,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>26</v>
       </c>
@@ -2205,7 +2206,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>26</v>
       </c>
@@ -2261,7 +2262,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>26</v>
       </c>
@@ -2317,7 +2318,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>26</v>
       </c>
@@ -2373,7 +2374,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>26</v>
       </c>
@@ -2429,7 +2430,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>26</v>
       </c>
@@ -2485,7 +2486,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>26</v>
       </c>
@@ -2541,7 +2542,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>26</v>
       </c>
@@ -2597,7 +2598,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>26</v>
       </c>
@@ -2653,7 +2654,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="51">
         <v>2024</v>
       </c>
@@ -2707,7 +2708,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>26</v>
       </c>
@@ -2763,7 +2764,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>26</v>
       </c>
@@ -2819,7 +2820,7 @@
         <v>5.41</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="49">
         <v>2023</v>
       </c>
@@ -2873,7 +2874,7 @@
         <v>5.82</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="51">
         <v>2022</v>
       </c>
@@ -2927,7 +2928,7 @@
         <v>6.65</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="49">
         <v>2021</v>
       </c>
@@ -2981,7 +2982,7 @@
         <v>5.33</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="51">
         <v>2020</v>
       </c>
@@ -3035,7 +3036,7 @@
         <v>4.84</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="49">
         <v>2019</v>
       </c>
@@ -3089,7 +3090,7 @@
         <v>4.01</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="51">
         <v>2018</v>
       </c>
@@ -3143,7 +3144,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="49" t="s">
         <v>59</v>
       </c>
